--- a/consent_forms/025_dental_records_release_form--consent_forms.xlsx
+++ b/consent_forms/025_dental_records_release_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patient_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Patient's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthcare_provider</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Healthcare Provider</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Name of the healthcare provider</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,38 +574,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>healthcare_provider_name</t>
+          <t>reason_for_requesting_records</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthcare_provider</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Reason for Requesting Records</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Reason for requesting the patient's dental records</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reason_for_requesting_records</t>
+          <t>patient_signature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reason_for_requesting_records</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Patient Signature</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sign here to confirm</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,89 +623,105 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>patient_signature</t>
+          <t>date_of_request</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>patient_signature</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date of Request</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Date when requesting the patient's dental records</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_request</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date_of_request</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Address to send the records to</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date_received</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date_received</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Contact number</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>medical_group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Medical Group</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Are you a part of a medical group?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>doctor_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Doctor's Name</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Name of the doctor providing care</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>doctor_specialty</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Doctor's Specialty</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Specialty of the doctor providing care</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,38 +790,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>patient_age</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Patient Age</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Age of the patient</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_group</t>
+          <t>patient_sex</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical_group</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Patient Sex</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sex of the patient</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -791,23 +839,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_group_label</t>
+          <t>medical_record_id</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical_group</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Medical Record ID</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ID of the patient's medical record</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>doctor_name</t>
+          <t>patient_medical_record</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>doctor_name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Patient Medical Record</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Medical record number</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,23 +893,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>doctor_specialty</t>
+          <t>patient_race</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>doctor_specialty</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Patient Race</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Race of the patient</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>doctor_id</t>
+          <t>doctor_medical_record</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>doctor_id</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Doctor Medical Record</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Medical record number</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>patient_age</t>
+          <t>patient_medical_record_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>patient_age</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Patient Medical Record 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Medical record number</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>patient_sex</t>
+          <t>doctor_specialty_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>patient_sex</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Doctor Specialty 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Specialty of the doctor providing care</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>patient_race</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>patient_race</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_record_id</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>medical_record_id</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>patient_medical_record</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>patient_medical_record</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>medical_provider_medical_record</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>medical_provider_medical_record</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_medical_record</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>patient_medical_record</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>doctor_medical_record</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>doctor_medical_record</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>patient_medical_record_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>patient_medical_record_2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1042,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,80 +1059,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medical_group_label_choices</t>
+          <t>patient_sex_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_group_label_choices</t>
+          <t>patient_sex_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>patient_sex_choices</t>
+          <t>patient_race_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>patient_sex_choices</t>
+          <t>patient_race_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1144,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>patient_race_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
